--- a/feedback_forms/027_streaming_service_engagement_report_form--feedback_forms.xlsx
+++ b/feedback_forms/027_streaming_service_engagement_report_form--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,18 +520,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_select</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What's your preferred category?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select one option</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,10 +552,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What's your name?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please provide your full name</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>yes</t>
@@ -571,10 +579,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What's your email?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please provide a valid email address</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>yes</t>
@@ -584,23 +596,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>channel_watched</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How often do you watch the channel?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Select one option</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,41 +628,49 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>channel_watch_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Feedback</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please provide your name for channel</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>email_chan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>How often do you watch the channel?</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please provide a valid email address for channel</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,18 +682,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Additional comments</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -681,38 +709,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>channel_feedback</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>Feedback about channel</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please provide any feedback</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>categories_select_multiple</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Feedback</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Select categories</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select multiple options</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -722,20 +758,24 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>channel_name_again</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Channel Name Again</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please provide your name again</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>email_chan_again</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Email Chan Again</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please provide a valid email address again</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>yes</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>channel_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,15 +844,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>channel_feedback_again</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Please provide any feedback</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>no</t>
@@ -814,21 +866,133 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>channel_cat_select_multiple_again</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Channel Cat Select Multiple Again</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Select multiple options</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>text</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>feedback</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Feedback</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>channel_name_again_again</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Channel Name Again Again</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Please provide your name again</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>email_chan_again_again</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Email Chan Again Again</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Please provide a valid email address again</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>channel_additional_comments</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Channel Additional Comments</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Please provide any additional comments</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>channel_final_feedback</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Final feedback</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Please provide any final feedback</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -845,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -873,153 +1037,272 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_select_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>select_category</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Select Category</t>
+          <t>Sports</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_select_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>select_category_1</t>
+          <t>entertainment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Select Category 1</t>
+          <t>Entertainment</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_select_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>select_category_2</t>
+          <t>music</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Select Category 2</t>
+          <t>Music</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_select_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>select_option_1</t>
+          <t>gaming</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Select Option 1</t>
+          <t>Gaming</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>channel_watched_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>select_option_2</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Select Option 2</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>channel_watched_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>select_option_3</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Select Option 3</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>channel_watched_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>select_category_1</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Select Category 1</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>channel_watched_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>select_category_2</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Select Category 2</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>categories_select_multiple_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>select_category_3</t>
+          <t>sports</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Select Category 3</t>
+          <t>Sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>categories_select_multiple_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>categories_select_multiple_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>music</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>categories_select_multiple_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>gaming</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gaming</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>channel_cat_select_multiple_again_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sports</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>channel_cat_select_multiple_again_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>entertainment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>channel_cat_select_multiple_again_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>music</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Music</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>channel_cat_select_multiple_again_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>gaming</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Gaming</t>
         </is>
       </c>
     </row>
